--- a/results/att_evalue_survey.xlsx
+++ b/results/att_evalue_survey.xlsx
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5002094490957281</v>
+        <v>0.499321025741696</v>
       </c>
       <c r="D2" t="n">
-        <v>1.576473828227016</v>
+        <v>1.575199818981436</v>
       </c>
       <c r="E2" t="n">
-        <v>2.529781702346247</v>
+        <v>2.527068849225468</v>
       </c>
       <c r="F2" t="n">
-        <v>2.066107480472872</v>
+        <v>2.071911862906454</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.158943053597389e-29</v>
+        <v>4.216315028049169e-31</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.04399205111521829</v>
+        <v>-0.04256676218162255</v>
       </c>
       <c r="D3" t="n">
-        <v>1.040844878492812</v>
+        <v>1.039495764326115</v>
       </c>
       <c r="E3" t="n">
-        <v>1.247032129776456</v>
+        <v>1.242117776274024</v>
       </c>
       <c r="F3" t="n">
-        <v>1.486457574263708</v>
+        <v>1.48080696435236</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,11 +550,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>E-value = 1.25. This effect is highly sensitive to unmeasured confounding and could easily be explained by a weak confounder. The E-value for the confidence interval bound is 1.49, meaning a confounder of this strength could shift the CI to include the null.</t>
+          <t>E-value = 1.24. This effect is highly sensitive to unmeasured confounding and could easily be explained by a weak confounder. The E-value for the confidence interval bound is 1.48, meaning a confounder of this strength could shift the CI to include the null.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.2407582275589254</v>
+        <v>0.2414710814149404</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2953172367768869</v>
+        <v>0.295112936491181</v>
       </c>
       <c r="D4" t="n">
-        <v>1.308313215116436</v>
+        <v>1.308070004950221</v>
       </c>
       <c r="E4" t="n">
-        <v>1.943427577835364</v>
+        <v>1.942874804002851</v>
       </c>
       <c r="F4" t="n">
-        <v>1.659758406166924</v>
+        <v>1.646301908670703</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -590,11 +590,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E-value = 1.94. A relatively weak unmeasured confounder (RR ≈ 1.94) could potentially explain this effect. Interpret with caution. The E-value for the confidence interval bound is 1.66, meaning a confounder of this strength could shift the CI to include the null.</t>
+          <t>E-value = 1.94. A relatively weak unmeasured confounder (RR ≈ 1.94) could potentially explain this effect. Interpret with caution. The E-value for the confidence interval bound is 1.65, meaning a confounder of this strength could shift the CI to include the null.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.553841777150192e-13</v>
+        <v>9.590676754514887e-12</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
